--- a/output/pdf_financials_xlsx/CAMP.xlsx
+++ b/output/pdf_financials_xlsx/CAMP.xlsx
@@ -1942,13 +1942,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.996812</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.996812</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.999914</v>
       </c>
     </row>
     <row r="93">
@@ -3037,7 +3037,11 @@
           <t>Reserve 9</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>-</t>
@@ -3361,7 +3365,11 @@
           <t>Reserve 10</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E22" s="5" t="n">
         <v>0.996812</v>
       </c>

--- a/output/pdf_financials_xlsx/CAMP.xlsx
+++ b/output/pdf_financials_xlsx/CAMP.xlsx
@@ -577,13 +577,13 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.139824</v>
+        <v>0.247592</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.114865</v>
+        <v>0.338232</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.096413</v>
+        <v>0.881425</v>
       </c>
     </row>
     <row r="11">
@@ -593,13 +593,13 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-0.139824</v>
+        <v>-0.247592</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.114865</v>
+        <v>-0.338232</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.096413</v>
+        <v>-0.881425</v>
       </c>
     </row>
     <row r="12">
@@ -609,10 +609,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.016959</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>4.2e-05</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
@@ -867,10 +867,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-2.009429</v>
+        <v>-2.026388</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.33919</v>
+        <v>-0.339232</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-0.875425</v>
@@ -899,10 +899,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-2.009429</v>
+        <v>-2.026388</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.33919</v>
+        <v>-0.339232</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-0.875425</v>
@@ -982,13 +982,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.034291</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.002222</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.389543</v>
       </c>
     </row>
     <row r="35">
@@ -1014,13 +1014,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0.005</v>
+        <v>0.039291</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.004</v>
+        <v>0.006222</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0.01</v>
+        <v>0.399543</v>
       </c>
     </row>
     <row r="37">
@@ -2721,7 +2721,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -4819,7 +4819,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4943,17 +4943,17 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E72" s="5" t="n">
-        <v>-0.247592</v>
+        <v>0.247592</v>
       </c>
       <c r="F72" s="5" t="n">
-        <v>-0.338232</v>
+        <v>0.338232</v>
       </c>
       <c r="G72" s="5" t="n">
-        <v>-0.881425</v>
+        <v>0.881425</v>
       </c>
     </row>
     <row r="73">
@@ -4974,7 +4974,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E73" s="5" t="n">
@@ -5408,7 +5408,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">

--- a/output/pdf_financials_xlsx/CAMP.xlsx
+++ b/output/pdf_financials_xlsx/CAMP.xlsx
@@ -1480,13 +1480,13 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>0</v>
+        <v>0.082648</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>0.113278</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>0.2902</v>
       </c>
     </row>
     <row r="65">
@@ -1528,13 +1528,13 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.03372</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.171055</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.36717</v>
       </c>
     </row>
     <row r="68">
